--- a/artfynd/A 51217-2024 artfynd.xlsx
+++ b/artfynd/A 51217-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56226441</v>
+        <v>111050634</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +686,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Etapp 15:2, Sörmlandsleden 350 m OSO Millsätter, Srm</t>
+          <t>Vinterled, Vinterled, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622635.594245782</v>
+        <v>622350</v>
       </c>
       <c r="R2" t="n">
-        <v>6563244.954182563</v>
+        <v>6562740</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -744,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-12-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-12-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mindre bestånd intill leden.</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,23 +766,124 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Mager o torr mark intill kalhygge.</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Tomas Järnetun</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tomas Järnetun</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>56226441</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Etapp 15:2, Sörmlandsleden 350 m OSO Millsätter, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>622636</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6563245</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gåsinge-Dillnäs</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-12-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-12-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mindre bestånd intill leden.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Mager o torr mark intill kalhygge.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Rolf Wahlström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Rolf Wahlström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51217-2024 artfynd.xlsx
+++ b/artfynd/A 51217-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111050634</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,8 +894,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56226441</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>